--- a/output/yearly_population_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_24_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5075</v>
+        <v>5774</v>
       </c>
       <c r="C2" t="n">
-        <v>7140</v>
+        <v>4804</v>
       </c>
       <c r="D2" t="n">
-        <v>19779</v>
+        <v>19942</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3564</v>
+        <v>3804</v>
       </c>
       <c r="C3" t="n">
-        <v>4492</v>
+        <v>3859</v>
       </c>
       <c r="D3" t="n">
-        <v>13448</v>
+        <v>13057</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2735</v>
+        <v>3086</v>
       </c>
       <c r="C4" t="n">
-        <v>5947</v>
+        <v>4339</v>
       </c>
       <c r="D4" t="n">
-        <v>6728</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1779</v>
+        <v>2039</v>
       </c>
       <c r="C5" t="n">
-        <v>4669</v>
+        <v>3283</v>
       </c>
       <c r="D5" t="n">
-        <v>2720</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>1187</v>
       </c>
       <c r="C6" t="n">
-        <v>2680</v>
+        <v>1786</v>
       </c>
       <c r="D6" t="n">
-        <v>1206</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>446</v>
+        <v>562</v>
       </c>
       <c r="C7" t="n">
-        <v>1506</v>
+        <v>957</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="C8" t="n">
-        <v>760</v>
+        <v>521</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6738</v>
+        <v>7296</v>
       </c>
       <c r="C2" t="n">
-        <v>6821</v>
+        <v>7350</v>
       </c>
       <c r="D2" t="n">
-        <v>25828</v>
+        <v>18504</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3466</v>
+        <v>3893</v>
       </c>
       <c r="C3" t="n">
-        <v>5026</v>
+        <v>3778</v>
       </c>
       <c r="D3" t="n">
-        <v>13405</v>
+        <v>13150</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2650</v>
+        <v>2924</v>
       </c>
       <c r="C4" t="n">
-        <v>5110</v>
+        <v>3962</v>
       </c>
       <c r="D4" t="n">
-        <v>7555</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1941</v>
+        <v>2223</v>
       </c>
       <c r="C5" t="n">
-        <v>5128</v>
+        <v>3741</v>
       </c>
       <c r="D5" t="n">
-        <v>3291</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1199</v>
+        <v>1449</v>
       </c>
       <c r="C6" t="n">
-        <v>3569</v>
+        <v>2468</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>591</v>
+        <v>755</v>
       </c>
       <c r="C7" t="n">
-        <v>2019</v>
+        <v>1354</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>329</v>
       </c>
       <c r="C8" t="n">
-        <v>1088</v>
+        <v>721</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>388</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7654</v>
+        <v>9712</v>
       </c>
       <c r="C2" t="n">
-        <v>7450</v>
+        <v>12598</v>
       </c>
       <c r="D2" t="n">
-        <v>29479</v>
+        <v>19889</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3903</v>
+        <v>4350</v>
       </c>
       <c r="C3" t="n">
-        <v>5121</v>
+        <v>4730</v>
       </c>
       <c r="D3" t="n">
-        <v>14115</v>
+        <v>12994</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>2854</v>
       </c>
       <c r="C4" t="n">
-        <v>4965</v>
+        <v>3755</v>
       </c>
       <c r="D4" t="n">
-        <v>8223</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2005</v>
+        <v>2249</v>
       </c>
       <c r="C5" t="n">
-        <v>4964</v>
+        <v>3765</v>
       </c>
       <c r="D5" t="n">
-        <v>3773</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1365</v>
+        <v>1644</v>
       </c>
       <c r="C6" t="n">
-        <v>4194</v>
+        <v>2982</v>
       </c>
       <c r="D6" t="n">
-        <v>1662</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>748</v>
+        <v>941</v>
       </c>
       <c r="C7" t="n">
-        <v>2636</v>
+        <v>1831</v>
       </c>
       <c r="D7" t="n">
-        <v>821</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342</v>
+        <v>448</v>
       </c>
       <c r="C8" t="n">
-        <v>1450</v>
+        <v>993</v>
       </c>
       <c r="D8" t="n">
-        <v>494</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="C9" t="n">
-        <v>742</v>
+        <v>521</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6963</v>
+        <v>8597</v>
       </c>
       <c r="C2" t="n">
-        <v>5006</v>
+        <v>8163</v>
       </c>
       <c r="D2" t="n">
-        <v>24125</v>
+        <v>16126</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4667</v>
+        <v>5322</v>
       </c>
       <c r="C3" t="n">
-        <v>7823</v>
+        <v>7861</v>
       </c>
       <c r="D3" t="n">
-        <v>15455</v>
+        <v>14579</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1852</v>
+        <v>2078</v>
       </c>
       <c r="C4" t="n">
-        <v>7577</v>
+        <v>5813</v>
       </c>
       <c r="D4" t="n">
-        <v>8018</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1261</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>4110</v>
+        <v>2922</v>
       </c>
       <c r="D5" t="n">
-        <v>2679</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>2583</v>
+        <v>1794</v>
       </c>
       <c r="D6" t="n">
-        <v>804</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>1421</v>
+        <v>973</v>
       </c>
       <c r="D7" t="n">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C8" t="n">
-        <v>727</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4271</v>
+        <v>5123</v>
       </c>
       <c r="C2" t="n">
-        <v>2325</v>
+        <v>3616</v>
       </c>
       <c r="D2" t="n">
-        <v>17400</v>
+        <v>12565</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4868</v>
+        <v>5814</v>
       </c>
       <c r="C3" t="n">
-        <v>5877</v>
+        <v>7214</v>
       </c>
       <c r="D3" t="n">
-        <v>15743</v>
+        <v>13938</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2559</v>
+        <v>2952</v>
       </c>
       <c r="C4" t="n">
-        <v>7828</v>
+        <v>6937</v>
       </c>
       <c r="D4" t="n">
-        <v>9070</v>
+        <v>8903</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1412</v>
+        <v>1674</v>
       </c>
       <c r="C5" t="n">
-        <v>5686</v>
+        <v>4278</v>
       </c>
       <c r="D5" t="n">
-        <v>3315</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>1053</v>
       </c>
       <c r="C6" t="n">
-        <v>3257</v>
+        <v>2307</v>
       </c>
       <c r="D6" t="n">
-        <v>997</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>402</v>
       </c>
       <c r="C7" t="n">
-        <v>1876</v>
+        <v>1307</v>
       </c>
       <c r="D7" t="n">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>958</v>
+        <v>674</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4626</v>
+        <v>5925</v>
       </c>
       <c r="C2" t="n">
-        <v>5244</v>
+        <v>3326</v>
       </c>
       <c r="D2" t="n">
-        <v>23715</v>
+        <v>16422</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3867</v>
+        <v>4659</v>
       </c>
       <c r="C3" t="n">
-        <v>3693</v>
+        <v>4707</v>
       </c>
       <c r="D3" t="n">
-        <v>14898</v>
+        <v>12881</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3091</v>
+        <v>3638</v>
       </c>
       <c r="C4" t="n">
-        <v>6691</v>
+        <v>7005</v>
       </c>
       <c r="D4" t="n">
-        <v>9947</v>
+        <v>9502</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1694</v>
+        <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>6595</v>
+        <v>5516</v>
       </c>
       <c r="D5" t="n">
-        <v>4153</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>1235</v>
       </c>
       <c r="C6" t="n">
-        <v>4375</v>
+        <v>3251</v>
       </c>
       <c r="D6" t="n">
-        <v>1339</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>596</v>
       </c>
       <c r="C7" t="n">
-        <v>2502</v>
+        <v>1779</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>208</v>
       </c>
       <c r="C8" t="n">
-        <v>1344</v>
+        <v>953</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>619</v>
+        <v>484</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>38</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2712</v>
+        <v>3410</v>
       </c>
       <c r="C2" t="n">
-        <v>2429</v>
+        <v>1469</v>
       </c>
       <c r="D2" t="n">
-        <v>16393</v>
+        <v>11213</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3910</v>
+        <v>4811</v>
       </c>
       <c r="C3" t="n">
-        <v>4108</v>
+        <v>4025</v>
       </c>
       <c r="D3" t="n">
-        <v>15527</v>
+        <v>12976</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3425</v>
+        <v>4088</v>
       </c>
       <c r="C4" t="n">
-        <v>6186</v>
+        <v>6760</v>
       </c>
       <c r="D4" t="n">
-        <v>10597</v>
+        <v>10117</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1774</v>
+        <v>2137</v>
       </c>
       <c r="C5" t="n">
-        <v>7536</v>
+        <v>6563</v>
       </c>
       <c r="D5" t="n">
-        <v>4500</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>827</v>
+        <v>1087</v>
       </c>
       <c r="C6" t="n">
-        <v>5319</v>
+        <v>4104</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>2587</v>
+        <v>1854</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1028</v>
+        <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3582</v>
+        <v>4471</v>
       </c>
       <c r="C2" t="n">
-        <v>4589</v>
+        <v>5088</v>
       </c>
       <c r="D2" t="n">
-        <v>16773</v>
+        <v>11339</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2910</v>
+        <v>3577</v>
       </c>
       <c r="C3" t="n">
-        <v>2962</v>
+        <v>2450</v>
       </c>
       <c r="D3" t="n">
-        <v>14601</v>
+        <v>11829</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3170</v>
+        <v>3881</v>
       </c>
       <c r="C4" t="n">
-        <v>5059</v>
+        <v>5292</v>
       </c>
       <c r="D4" t="n">
-        <v>11079</v>
+        <v>10303</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2177</v>
+        <v>2626</v>
       </c>
       <c r="C5" t="n">
-        <v>6829</v>
+        <v>6584</v>
       </c>
       <c r="D5" t="n">
-        <v>5299</v>
+        <v>5283</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1091</v>
+        <v>1374</v>
       </c>
       <c r="C6" t="n">
-        <v>6278</v>
+        <v>5213</v>
       </c>
       <c r="D6" t="n">
-        <v>1773</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>436</v>
       </c>
       <c r="C7" t="n">
-        <v>3761</v>
+        <v>2859</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>1628</v>
+        <v>1222</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>543</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2388</v>
+        <v>3369</v>
       </c>
       <c r="C2" t="n">
-        <v>2740</v>
+        <v>3707</v>
       </c>
       <c r="D2" t="n">
-        <v>12319</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2742</v>
+        <v>3401</v>
       </c>
       <c r="C3" t="n">
-        <v>3309</v>
+        <v>3223</v>
       </c>
       <c r="D3" t="n">
-        <v>14067</v>
+        <v>11103</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2848</v>
+        <v>3485</v>
       </c>
       <c r="C4" t="n">
-        <v>4185</v>
+        <v>4079</v>
       </c>
       <c r="D4" t="n">
-        <v>11321</v>
+        <v>10308</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2351</v>
+        <v>2864</v>
       </c>
       <c r="C5" t="n">
-        <v>6286</v>
+        <v>6191</v>
       </c>
       <c r="D5" t="n">
-        <v>5905</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1300</v>
+        <v>1639</v>
       </c>
       <c r="C6" t="n">
-        <v>6716</v>
+        <v>5890</v>
       </c>
       <c r="D6" t="n">
-        <v>2091</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>4658</v>
+        <v>3699</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2147</v>
+        <v>1643</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>579</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4074</v>
+        <v>6166</v>
       </c>
       <c r="C2" t="n">
-        <v>7667</v>
+        <v>10694</v>
       </c>
       <c r="D2" t="n">
-        <v>16780</v>
+        <v>13121</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2197</v>
+        <v>2845</v>
       </c>
       <c r="C3" t="n">
-        <v>2755</v>
+        <v>3032</v>
       </c>
       <c r="D3" t="n">
-        <v>13055</v>
+        <v>10143</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2441</v>
+        <v>3030</v>
       </c>
       <c r="C4" t="n">
-        <v>3679</v>
+        <v>3599</v>
       </c>
       <c r="D4" t="n">
-        <v>11263</v>
+        <v>10116</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2326</v>
+        <v>2815</v>
       </c>
       <c r="C5" t="n">
-        <v>5328</v>
+        <v>5189</v>
       </c>
       <c r="D5" t="n">
-        <v>6505</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1547</v>
+        <v>1944</v>
       </c>
       <c r="C6" t="n">
-        <v>6488</v>
+        <v>5961</v>
       </c>
       <c r="D6" t="n">
-        <v>2576</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>552</v>
+        <v>762</v>
       </c>
       <c r="C7" t="n">
-        <v>5442</v>
+        <v>4577</v>
       </c>
       <c r="D7" t="n">
-        <v>926</v>
+        <v>981</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>3077</v>
+        <v>2444</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>1149</v>
+        <v>959</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5165</v>
+        <v>7024</v>
       </c>
       <c r="C2" t="n">
-        <v>5859</v>
+        <v>3589</v>
       </c>
       <c r="D2" t="n">
-        <v>13649</v>
+        <v>10506</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2882</v>
+        <v>4266</v>
       </c>
       <c r="C2" t="n">
-        <v>4294</v>
+        <v>5817</v>
       </c>
       <c r="D2" t="n">
-        <v>12351</v>
+        <v>9552</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3011</v>
+        <v>4018</v>
       </c>
       <c r="C3" t="n">
-        <v>4167</v>
+        <v>5240</v>
       </c>
       <c r="D3" t="n">
-        <v>14363</v>
+        <v>11264</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3394</v>
+        <v>4149</v>
       </c>
       <c r="C4" t="n">
-        <v>5434</v>
+        <v>5307</v>
       </c>
       <c r="D4" t="n">
-        <v>11554</v>
+        <v>10583</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1515</v>
+        <v>1926</v>
       </c>
       <c r="C5" t="n">
-        <v>8552</v>
+        <v>8034</v>
       </c>
       <c r="D5" t="n">
-        <v>6008</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>510</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>6668</v>
+        <v>5829</v>
       </c>
       <c r="D6" t="n">
-        <v>2042</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>3015</v>
+        <v>2395</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1126</v>
+        <v>939</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5791</v>
+        <v>6966</v>
       </c>
       <c r="C2" t="n">
-        <v>5828</v>
+        <v>2472</v>
       </c>
       <c r="D2" t="n">
-        <v>14798</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2195</v>
+        <v>2983</v>
       </c>
       <c r="C3" t="n">
-        <v>2952</v>
+        <v>1808</v>
       </c>
       <c r="D3" t="n">
-        <v>2932</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4068</v>
+        <v>4640</v>
       </c>
       <c r="C2" t="n">
-        <v>3208</v>
+        <v>3704</v>
       </c>
       <c r="D2" t="n">
-        <v>21250</v>
+        <v>19894</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3279</v>
+        <v>4087</v>
       </c>
       <c r="C3" t="n">
-        <v>3949</v>
+        <v>1885</v>
       </c>
       <c r="D3" t="n">
-        <v>4709</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>987</v>
+        <v>1329</v>
       </c>
       <c r="C4" t="n">
-        <v>1773</v>
+        <v>1119</v>
       </c>
       <c r="D4" t="n">
-        <v>1772</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5003</v>
+        <v>5544</v>
       </c>
       <c r="C2" t="n">
-        <v>6382</v>
+        <v>2775</v>
       </c>
       <c r="D2" t="n">
-        <v>20281</v>
+        <v>18916</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3019</v>
+        <v>3631</v>
       </c>
       <c r="C3" t="n">
-        <v>3068</v>
+        <v>2490</v>
       </c>
       <c r="D3" t="n">
-        <v>7016</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1806</v>
+        <v>2295</v>
       </c>
       <c r="C4" t="n">
-        <v>2968</v>
+        <v>1518</v>
       </c>
       <c r="D4" t="n">
-        <v>2282</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>466</v>
+        <v>605</v>
       </c>
       <c r="C5" t="n">
-        <v>1063</v>
+        <v>715</v>
       </c>
       <c r="D5" t="n">
-        <v>1245</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5628</v>
+        <v>6744</v>
       </c>
       <c r="C2" t="n">
-        <v>8261</v>
+        <v>6668</v>
       </c>
       <c r="D2" t="n">
-        <v>22562</v>
+        <v>18115</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3244</v>
+        <v>3768</v>
       </c>
       <c r="C3" t="n">
-        <v>4176</v>
+        <v>2293</v>
       </c>
       <c r="D3" t="n">
-        <v>8538</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2039</v>
+        <v>2509</v>
       </c>
       <c r="C4" t="n">
-        <v>2960</v>
+        <v>2018</v>
       </c>
       <c r="D4" t="n">
-        <v>3054</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>948</v>
+        <v>1206</v>
       </c>
       <c r="C5" t="n">
-        <v>2046</v>
+        <v>1117</v>
       </c>
       <c r="D5" t="n">
-        <v>1396</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>686</v>
+        <v>513</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6644</v>
+        <v>6573</v>
       </c>
       <c r="C2" t="n">
-        <v>10931</v>
+        <v>7543</v>
       </c>
       <c r="D2" t="n">
-        <v>21488</v>
+        <v>24547</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3216</v>
+        <v>3809</v>
       </c>
       <c r="C3" t="n">
-        <v>5160</v>
+        <v>3795</v>
       </c>
       <c r="D3" t="n">
-        <v>9472</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1650</v>
+        <v>1947</v>
       </c>
       <c r="C4" t="n">
-        <v>2987</v>
+        <v>1766</v>
       </c>
       <c r="D4" t="n">
-        <v>3430</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>780</v>
+        <v>979</v>
       </c>
       <c r="C5" t="n">
-        <v>1846</v>
+        <v>1172</v>
       </c>
       <c r="D5" t="n">
-        <v>1342</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>919</v>
+        <v>552</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4912</v>
+        <v>5789</v>
       </c>
       <c r="C2" t="n">
-        <v>7167</v>
+        <v>5632</v>
       </c>
       <c r="D2" t="n">
-        <v>26728</v>
+        <v>24117</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4158</v>
+        <v>4384</v>
       </c>
       <c r="C3" t="n">
-        <v>7379</v>
+        <v>5197</v>
       </c>
       <c r="D3" t="n">
-        <v>10874</v>
+        <v>10744</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2127</v>
+        <v>2532</v>
       </c>
       <c r="C4" t="n">
-        <v>4259</v>
+        <v>2995</v>
       </c>
       <c r="D4" t="n">
-        <v>4601</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1091</v>
+        <v>1322</v>
       </c>
       <c r="C5" t="n">
-        <v>2486</v>
+        <v>1506</v>
       </c>
       <c r="D5" t="n">
-        <v>1722</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>497</v>
+        <v>636</v>
       </c>
       <c r="C6" t="n">
-        <v>1441</v>
+        <v>902</v>
       </c>
       <c r="D6" t="n">
-        <v>868</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>661</v>
+        <v>439</v>
       </c>
       <c r="D7" t="n">
         <v>566</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6241,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5015</v>
+        <v>5070</v>
       </c>
       <c r="C2" t="n">
-        <v>4052</v>
+        <v>4214</v>
       </c>
       <c r="D2" t="n">
-        <v>23879</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3736</v>
+        <v>4192</v>
       </c>
       <c r="C3" t="n">
-        <v>6273</v>
+        <v>4694</v>
       </c>
       <c r="D3" t="n">
-        <v>12627</v>
+        <v>12199</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2713</v>
+        <v>2983</v>
       </c>
       <c r="C4" t="n">
-        <v>5967</v>
+        <v>4193</v>
       </c>
       <c r="D4" t="n">
-        <v>5621</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1404</v>
+        <v>1713</v>
       </c>
       <c r="C5" t="n">
-        <v>3421</v>
+        <v>2332</v>
       </c>
       <c r="D5" t="n">
-        <v>2222</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>726</v>
+        <v>903</v>
       </c>
       <c r="C6" t="n">
-        <v>1986</v>
+        <v>1227</v>
       </c>
       <c r="D6" t="n">
-        <v>1011</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="C7" t="n">
-        <v>1067</v>
+        <v>692</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>478</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_24_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5774</v>
+        <v>5904</v>
       </c>
       <c r="C2" t="n">
-        <v>4804</v>
+        <v>9522</v>
       </c>
       <c r="D2" t="n">
-        <v>19942</v>
+        <v>19119</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3804</v>
+        <v>3684</v>
       </c>
       <c r="C3" t="n">
-        <v>3859</v>
+        <v>8573</v>
       </c>
       <c r="D3" t="n">
-        <v>13057</v>
+        <v>9485</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3086</v>
+        <v>3063</v>
       </c>
       <c r="C4" t="n">
-        <v>4339</v>
+        <v>7574</v>
       </c>
       <c r="D4" t="n">
-        <v>6446</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2039</v>
+        <v>2151</v>
       </c>
       <c r="C5" t="n">
-        <v>3283</v>
+        <v>5427</v>
       </c>
       <c r="D5" t="n">
-        <v>2614</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1187</v>
+        <v>1239</v>
       </c>
       <c r="C6" t="n">
-        <v>1786</v>
+        <v>3690</v>
       </c>
       <c r="D6" t="n">
-        <v>1153</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C7" t="n">
-        <v>957</v>
+        <v>2389</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C8" t="n">
-        <v>521</v>
+        <v>1263</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>512</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7296</v>
+        <v>8857</v>
       </c>
       <c r="C2" t="n">
-        <v>7350</v>
+        <v>9766</v>
       </c>
       <c r="D2" t="n">
-        <v>18504</v>
+        <v>17567</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3893</v>
+        <v>3772</v>
       </c>
       <c r="C3" t="n">
-        <v>3778</v>
+        <v>7936</v>
       </c>
       <c r="D3" t="n">
-        <v>13150</v>
+        <v>10095</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2924</v>
+        <v>2847</v>
       </c>
       <c r="C4" t="n">
-        <v>3962</v>
+        <v>7876</v>
       </c>
       <c r="D4" t="n">
-        <v>7330</v>
+        <v>5074</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2223</v>
+        <v>2269</v>
       </c>
       <c r="C5" t="n">
-        <v>3741</v>
+        <v>6210</v>
       </c>
       <c r="D5" t="n">
-        <v>3196</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1449</v>
+        <v>1468</v>
       </c>
       <c r="C6" t="n">
-        <v>2468</v>
+        <v>4369</v>
       </c>
       <c r="D6" t="n">
-        <v>1375</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C7" t="n">
-        <v>1354</v>
+        <v>2949</v>
       </c>
       <c r="D7" t="n">
-        <v>735</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="C8" t="n">
-        <v>721</v>
+        <v>1713</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C9" t="n">
-        <v>388</v>
+        <v>813</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9712</v>
+        <v>8774</v>
       </c>
       <c r="C2" t="n">
-        <v>12598</v>
+        <v>17271</v>
       </c>
       <c r="D2" t="n">
-        <v>19889</v>
+        <v>26705</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4350</v>
+        <v>4607</v>
       </c>
       <c r="C3" t="n">
-        <v>4730</v>
+        <v>7702</v>
       </c>
       <c r="D3" t="n">
-        <v>12994</v>
+        <v>10345</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2854</v>
+        <v>2733</v>
       </c>
       <c r="C4" t="n">
-        <v>3755</v>
+        <v>7661</v>
       </c>
       <c r="D4" t="n">
-        <v>8056</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2249</v>
+        <v>2232</v>
       </c>
       <c r="C5" t="n">
-        <v>3765</v>
+        <v>6692</v>
       </c>
       <c r="D5" t="n">
-        <v>3703</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1644</v>
+        <v>1621</v>
       </c>
       <c r="C6" t="n">
-        <v>2982</v>
+        <v>5056</v>
       </c>
       <c r="D6" t="n">
-        <v>1636</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C7" t="n">
-        <v>1831</v>
+        <v>3461</v>
       </c>
       <c r="D7" t="n">
-        <v>814</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="C8" t="n">
-        <v>993</v>
+        <v>2155</v>
       </c>
       <c r="D8" t="n">
-        <v>504</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>1131</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="D10" t="n">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>129</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8597</v>
+        <v>8127</v>
       </c>
       <c r="C2" t="n">
-        <v>8163</v>
+        <v>12158</v>
       </c>
       <c r="D2" t="n">
-        <v>16126</v>
+        <v>21860</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5322</v>
+        <v>5154</v>
       </c>
       <c r="C3" t="n">
-        <v>7861</v>
+        <v>12361</v>
       </c>
       <c r="D3" t="n">
-        <v>14579</v>
+        <v>11167</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2078</v>
+        <v>2062</v>
       </c>
       <c r="C4" t="n">
-        <v>5813</v>
+        <v>10469</v>
       </c>
       <c r="D4" t="n">
-        <v>7902</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1497</v>
       </c>
       <c r="C5" t="n">
-        <v>2922</v>
+        <v>4954</v>
       </c>
       <c r="D5" t="n">
-        <v>2669</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="C6" t="n">
-        <v>1794</v>
+        <v>3391</v>
       </c>
       <c r="D6" t="n">
-        <v>797</v>
+        <v>691</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="C7" t="n">
-        <v>973</v>
+        <v>2111</v>
       </c>
       <c r="D7" t="n">
-        <v>493</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>491</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
         <v>126</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5123</v>
+        <v>5036</v>
       </c>
       <c r="C2" t="n">
-        <v>3616</v>
+        <v>5381</v>
       </c>
       <c r="D2" t="n">
-        <v>12565</v>
+        <v>15916</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5814</v>
+        <v>5477</v>
       </c>
       <c r="C3" t="n">
-        <v>7214</v>
+        <v>11152</v>
       </c>
       <c r="D3" t="n">
-        <v>13938</v>
+        <v>12085</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2952</v>
+        <v>2784</v>
       </c>
       <c r="C4" t="n">
-        <v>6937</v>
+        <v>11506</v>
       </c>
       <c r="D4" t="n">
-        <v>8903</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1674</v>
+        <v>1638</v>
       </c>
       <c r="C5" t="n">
-        <v>4278</v>
+        <v>7259</v>
       </c>
       <c r="D5" t="n">
-        <v>3342</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1053</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>2307</v>
+        <v>4076</v>
       </c>
       <c r="D6" t="n">
-        <v>1008</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>354</v>
       </c>
       <c r="C7" t="n">
-        <v>1307</v>
+        <v>2622</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>674</v>
+        <v>1417</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>524</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5925</v>
+        <v>4799</v>
       </c>
       <c r="C2" t="n">
-        <v>3326</v>
+        <v>9111</v>
       </c>
       <c r="D2" t="n">
-        <v>16422</v>
+        <v>13216</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4659</v>
+        <v>4451</v>
       </c>
       <c r="C3" t="n">
-        <v>4707</v>
+        <v>7612</v>
       </c>
       <c r="D3" t="n">
-        <v>12881</v>
+        <v>11793</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3638</v>
+        <v>3360</v>
       </c>
       <c r="C4" t="n">
-        <v>7005</v>
+        <v>11100</v>
       </c>
       <c r="D4" t="n">
-        <v>9502</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
+        <v>1876</v>
       </c>
       <c r="C5" t="n">
-        <v>5516</v>
+        <v>9024</v>
       </c>
       <c r="D5" t="n">
-        <v>4115</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1235</v>
+        <v>1151</v>
       </c>
       <c r="C6" t="n">
-        <v>3251</v>
+        <v>5452</v>
       </c>
       <c r="D6" t="n">
-        <v>1385</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>596</v>
+        <v>524</v>
       </c>
       <c r="C7" t="n">
-        <v>1779</v>
+        <v>3219</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>953</v>
+        <v>1902</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>484</v>
+        <v>857</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3410</v>
+        <v>2930</v>
       </c>
       <c r="C2" t="n">
-        <v>1469</v>
+        <v>4420</v>
       </c>
       <c r="D2" t="n">
-        <v>11213</v>
+        <v>9211</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4811</v>
+        <v>4373</v>
       </c>
       <c r="C3" t="n">
-        <v>4025</v>
+        <v>7884</v>
       </c>
       <c r="D3" t="n">
-        <v>12976</v>
+        <v>11676</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4088</v>
+        <v>3699</v>
       </c>
       <c r="C4" t="n">
-        <v>6760</v>
+        <v>10863</v>
       </c>
       <c r="D4" t="n">
-        <v>10117</v>
+        <v>7553</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2137</v>
+        <v>1968</v>
       </c>
       <c r="C5" t="n">
-        <v>6563</v>
+        <v>10961</v>
       </c>
       <c r="D5" t="n">
-        <v>4451</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>930</v>
       </c>
       <c r="C6" t="n">
-        <v>4104</v>
+        <v>6247</v>
       </c>
       <c r="D6" t="n">
-        <v>1362</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>1854</v>
+        <v>3405</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>791</v>
+        <v>1380</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4471</v>
+        <v>3312</v>
       </c>
       <c r="C2" t="n">
-        <v>5088</v>
+        <v>4096</v>
       </c>
       <c r="D2" t="n">
-        <v>11339</v>
+        <v>11745</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>3224</v>
       </c>
       <c r="C3" t="n">
-        <v>2450</v>
+        <v>5708</v>
       </c>
       <c r="D3" t="n">
-        <v>11829</v>
+        <v>10594</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3881</v>
+        <v>3495</v>
       </c>
       <c r="C4" t="n">
-        <v>5292</v>
+        <v>9292</v>
       </c>
       <c r="D4" t="n">
-        <v>10303</v>
+        <v>7956</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2626</v>
+        <v>2344</v>
       </c>
       <c r="C5" t="n">
-        <v>6584</v>
+        <v>10795</v>
       </c>
       <c r="D5" t="n">
-        <v>5283</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>1190</v>
       </c>
       <c r="C6" t="n">
-        <v>5213</v>
+        <v>8153</v>
       </c>
       <c r="D6" t="n">
-        <v>1788</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>436</v>
+        <v>330</v>
       </c>
       <c r="C7" t="n">
-        <v>2859</v>
+        <v>4556</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1222</v>
+        <v>2101</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>656</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3369</v>
+        <v>2300</v>
       </c>
       <c r="C2" t="n">
-        <v>3707</v>
+        <v>3510</v>
       </c>
       <c r="D2" t="n">
-        <v>9300</v>
+        <v>9058</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3401</v>
+        <v>2852</v>
       </c>
       <c r="C3" t="n">
-        <v>3223</v>
+        <v>4664</v>
       </c>
       <c r="D3" t="n">
-        <v>11103</v>
+        <v>10163</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3485</v>
+        <v>3121</v>
       </c>
       <c r="C4" t="n">
-        <v>4079</v>
+        <v>7990</v>
       </c>
       <c r="D4" t="n">
-        <v>10308</v>
+        <v>8119</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2864</v>
+        <v>2552</v>
       </c>
       <c r="C5" t="n">
-        <v>6191</v>
+        <v>10376</v>
       </c>
       <c r="D5" t="n">
-        <v>5850</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1639</v>
+        <v>1368</v>
       </c>
       <c r="C6" t="n">
-        <v>5890</v>
+        <v>9261</v>
       </c>
       <c r="D6" t="n">
-        <v>2136</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>3699</v>
+        <v>5677</v>
       </c>
       <c r="D7" t="n">
-        <v>808</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1643</v>
+        <v>2667</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>579</v>
+        <v>712</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6166</v>
+        <v>3984</v>
       </c>
       <c r="C2" t="n">
-        <v>10694</v>
+        <v>8314</v>
       </c>
       <c r="D2" t="n">
-        <v>13121</v>
+        <v>9314</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2845</v>
+        <v>2247</v>
       </c>
       <c r="C3" t="n">
-        <v>3032</v>
+        <v>3776</v>
       </c>
       <c r="D3" t="n">
-        <v>10143</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3030</v>
+        <v>2660</v>
       </c>
       <c r="C4" t="n">
-        <v>3599</v>
+        <v>6482</v>
       </c>
       <c r="D4" t="n">
-        <v>10116</v>
+        <v>8146</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2815</v>
+        <v>2498</v>
       </c>
       <c r="C5" t="n">
-        <v>5189</v>
+        <v>9243</v>
       </c>
       <c r="D5" t="n">
-        <v>6314</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1944</v>
+        <v>1619</v>
       </c>
       <c r="C6" t="n">
-        <v>5961</v>
+        <v>9593</v>
       </c>
       <c r="D6" t="n">
-        <v>2586</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>762</v>
+        <v>536</v>
       </c>
       <c r="C7" t="n">
-        <v>4577</v>
+        <v>6939</v>
       </c>
       <c r="D7" t="n">
-        <v>981</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>2444</v>
+        <v>3695</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>959</v>
+        <v>1312</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7024</v>
+        <v>6602</v>
       </c>
       <c r="C2" t="n">
-        <v>3589</v>
+        <v>14212</v>
       </c>
       <c r="D2" t="n">
-        <v>10506</v>
+        <v>5423</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4266</v>
+        <v>2912</v>
       </c>
       <c r="C2" t="n">
-        <v>5817</v>
+        <v>4922</v>
       </c>
       <c r="D2" t="n">
-        <v>9552</v>
+        <v>6929</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4018</v>
+        <v>3107</v>
       </c>
       <c r="C3" t="n">
-        <v>5240</v>
+        <v>5126</v>
       </c>
       <c r="D3" t="n">
-        <v>11264</v>
+        <v>10175</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4149</v>
+        <v>3644</v>
       </c>
       <c r="C4" t="n">
-        <v>5307</v>
+        <v>9556</v>
       </c>
       <c r="D4" t="n">
-        <v>10583</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1926</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>8034</v>
+        <v>13570</v>
       </c>
       <c r="D5" t="n">
-        <v>5848</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>704</v>
+        <v>495</v>
       </c>
       <c r="C6" t="n">
-        <v>5829</v>
+        <v>8398</v>
       </c>
       <c r="D6" t="n">
-        <v>2119</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2395</v>
+        <v>3621</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>939</v>
+        <v>1285</v>
       </c>
       <c r="D8" t="n">
-        <v>308</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6966</v>
+        <v>8305</v>
       </c>
       <c r="C2" t="n">
-        <v>2472</v>
+        <v>6992</v>
       </c>
       <c r="D2" t="n">
-        <v>15480</v>
+        <v>8223</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2983</v>
+        <v>2804</v>
       </c>
       <c r="C3" t="n">
-        <v>1808</v>
+        <v>7162</v>
       </c>
       <c r="D3" t="n">
-        <v>2404</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4640</v>
+        <v>6019</v>
       </c>
       <c r="C2" t="n">
-        <v>3704</v>
+        <v>4955</v>
       </c>
       <c r="D2" t="n">
-        <v>19894</v>
+        <v>13481</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4087</v>
+        <v>4559</v>
       </c>
       <c r="C3" t="n">
-        <v>1885</v>
+        <v>6093</v>
       </c>
       <c r="D3" t="n">
-        <v>4423</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1329</v>
+        <v>1252</v>
       </c>
       <c r="C4" t="n">
-        <v>1119</v>
+        <v>4240</v>
       </c>
       <c r="D4" t="n">
-        <v>1665</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5544</v>
+        <v>7333</v>
       </c>
       <c r="C2" t="n">
-        <v>2775</v>
+        <v>6672</v>
       </c>
       <c r="D2" t="n">
-        <v>18916</v>
+        <v>15069</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3631</v>
+        <v>4340</v>
       </c>
       <c r="C3" t="n">
-        <v>2490</v>
+        <v>4755</v>
       </c>
       <c r="D3" t="n">
-        <v>6579</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2295</v>
+        <v>2468</v>
       </c>
       <c r="C4" t="n">
-        <v>1518</v>
+        <v>5142</v>
       </c>
       <c r="D4" t="n">
-        <v>2143</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>605</v>
+        <v>563</v>
       </c>
       <c r="C5" t="n">
-        <v>715</v>
+        <v>2416</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6744</v>
+        <v>6706</v>
       </c>
       <c r="C2" t="n">
-        <v>6668</v>
+        <v>11039</v>
       </c>
       <c r="D2" t="n">
-        <v>18115</v>
+        <v>17517</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3768</v>
+        <v>4695</v>
       </c>
       <c r="C3" t="n">
-        <v>2293</v>
+        <v>4989</v>
       </c>
       <c r="D3" t="n">
-        <v>7991</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2509</v>
+        <v>2857</v>
       </c>
       <c r="C4" t="n">
-        <v>2018</v>
+        <v>4781</v>
       </c>
       <c r="D4" t="n">
-        <v>2866</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="C5" t="n">
-        <v>1117</v>
+        <v>3778</v>
       </c>
       <c r="D5" t="n">
-        <v>1355</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>513</v>
+        <v>1355</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6573</v>
+        <v>6650</v>
       </c>
       <c r="C2" t="n">
-        <v>7543</v>
+        <v>10860</v>
       </c>
       <c r="D2" t="n">
-        <v>24547</v>
+        <v>16542</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>4107</v>
       </c>
       <c r="C3" t="n">
-        <v>3795</v>
+        <v>6574</v>
       </c>
       <c r="D3" t="n">
-        <v>8580</v>
+        <v>6523</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1947</v>
+        <v>2310</v>
       </c>
       <c r="C4" t="n">
-        <v>1766</v>
+        <v>4003</v>
       </c>
       <c r="D4" t="n">
-        <v>3215</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="C5" t="n">
-        <v>1172</v>
+        <v>3097</v>
       </c>
       <c r="D5" t="n">
-        <v>1288</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>552</v>
+        <v>1719</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>278</v>
+        <v>528</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5789</v>
+        <v>5753</v>
       </c>
       <c r="C2" t="n">
-        <v>5632</v>
+        <v>12032</v>
       </c>
       <c r="D2" t="n">
-        <v>24117</v>
+        <v>14228</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4384</v>
+        <v>4445</v>
       </c>
       <c r="C3" t="n">
-        <v>5197</v>
+        <v>7808</v>
       </c>
       <c r="D3" t="n">
-        <v>10744</v>
+        <v>7726</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2532</v>
+        <v>2803</v>
       </c>
       <c r="C4" t="n">
-        <v>2995</v>
+        <v>5474</v>
       </c>
       <c r="D4" t="n">
-        <v>4250</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1322</v>
+        <v>1482</v>
       </c>
       <c r="C5" t="n">
-        <v>1506</v>
+        <v>3563</v>
       </c>
       <c r="D5" t="n">
-        <v>1624</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="C6" t="n">
-        <v>902</v>
+        <v>2478</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
-        <v>439</v>
+        <v>1193</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>254</v>
+        <v>387</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>4804</v>
       </c>
       <c r="C2" t="n">
-        <v>4214</v>
+        <v>10930</v>
       </c>
       <c r="D2" t="n">
-        <v>23500</v>
+        <v>20988</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4192</v>
+        <v>4178</v>
       </c>
       <c r="C3" t="n">
-        <v>4694</v>
+        <v>8731</v>
       </c>
       <c r="D3" t="n">
-        <v>12199</v>
+        <v>8210</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2983</v>
+        <v>3083</v>
       </c>
       <c r="C4" t="n">
-        <v>4193</v>
+        <v>6659</v>
       </c>
       <c r="D4" t="n">
-        <v>5429</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1713</v>
+        <v>1875</v>
       </c>
       <c r="C5" t="n">
-        <v>2332</v>
+        <v>4516</v>
       </c>
       <c r="D5" t="n">
-        <v>2063</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>955</v>
       </c>
       <c r="C6" t="n">
-        <v>1227</v>
+        <v>2988</v>
       </c>
       <c r="D6" t="n">
-        <v>992</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C7" t="n">
-        <v>692</v>
+        <v>1859</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>789</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_24_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5904</v>
+        <v>827</v>
       </c>
       <c r="C2" t="n">
-        <v>9522</v>
+        <v>3657</v>
       </c>
       <c r="D2" t="n">
-        <v>19119</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3684</v>
+        <v>1338</v>
       </c>
       <c r="C3" t="n">
-        <v>8573</v>
+        <v>10236</v>
       </c>
       <c r="D3" t="n">
-        <v>9485</v>
+        <v>12991</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3063</v>
+        <v>869</v>
       </c>
       <c r="C4" t="n">
-        <v>7574</v>
+        <v>11311</v>
       </c>
       <c r="D4" t="n">
-        <v>4486</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2151</v>
+        <v>427</v>
       </c>
       <c r="C5" t="n">
-        <v>5427</v>
+        <v>5080</v>
       </c>
       <c r="D5" t="n">
-        <v>1875</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1239</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>3690</v>
+        <v>1935</v>
       </c>
       <c r="D6" t="n">
-        <v>970</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>568</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2389</v>
+        <v>755</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1263</v>
+        <v>359</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>512</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8857</v>
+        <v>946</v>
       </c>
       <c r="C2" t="n">
-        <v>9766</v>
+        <v>12454</v>
       </c>
       <c r="D2" t="n">
-        <v>17567</v>
+        <v>12806</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3772</v>
+        <v>937</v>
       </c>
       <c r="C3" t="n">
-        <v>7936</v>
+        <v>5991</v>
       </c>
       <c r="D3" t="n">
-        <v>10095</v>
+        <v>11703</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2847</v>
+        <v>935</v>
       </c>
       <c r="C4" t="n">
-        <v>7876</v>
+        <v>10606</v>
       </c>
       <c r="D4" t="n">
-        <v>5074</v>
+        <v>7443</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2269</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>6210</v>
+        <v>8144</v>
       </c>
       <c r="D5" t="n">
-        <v>2219</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1468</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>4369</v>
+        <v>3473</v>
       </c>
       <c r="D6" t="n">
-        <v>1078</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>753</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>2949</v>
+        <v>1317</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1713</v>
+        <v>537</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>813</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8774</v>
+        <v>510</v>
       </c>
       <c r="C2" t="n">
-        <v>17271</v>
+        <v>5329</v>
       </c>
       <c r="D2" t="n">
-        <v>26705</v>
+        <v>8769</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4607</v>
+        <v>904</v>
       </c>
       <c r="C3" t="n">
-        <v>7702</v>
+        <v>8191</v>
       </c>
       <c r="D3" t="n">
-        <v>10345</v>
+        <v>11535</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2733</v>
+        <v>1028</v>
       </c>
       <c r="C4" t="n">
-        <v>7661</v>
+        <v>9675</v>
       </c>
       <c r="D4" t="n">
-        <v>5642</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2232</v>
+        <v>561</v>
       </c>
       <c r="C5" t="n">
-        <v>6692</v>
+        <v>9819</v>
       </c>
       <c r="D5" t="n">
-        <v>2513</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1621</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>5056</v>
+        <v>4512</v>
       </c>
       <c r="D6" t="n">
-        <v>1217</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>927</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3461</v>
+        <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>412</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2155</v>
+        <v>496</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1131</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>502</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8127</v>
+        <v>453</v>
       </c>
       <c r="C2" t="n">
-        <v>12158</v>
+        <v>7865</v>
       </c>
       <c r="D2" t="n">
-        <v>21860</v>
+        <v>12122</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5154</v>
+        <v>626</v>
       </c>
       <c r="C3" t="n">
-        <v>12361</v>
+        <v>5997</v>
       </c>
       <c r="D3" t="n">
-        <v>11167</v>
+        <v>10343</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2062</v>
+        <v>857</v>
       </c>
       <c r="C4" t="n">
-        <v>10469</v>
+        <v>8811</v>
       </c>
       <c r="D4" t="n">
-        <v>5420</v>
+        <v>8385</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1497</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>4954</v>
+        <v>9639</v>
       </c>
       <c r="D5" t="n">
-        <v>1868</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>3391</v>
+        <v>6906</v>
       </c>
       <c r="D6" t="n">
-        <v>691</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>2111</v>
+        <v>2692</v>
       </c>
       <c r="D7" t="n">
-        <v>458</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1108</v>
+        <v>814</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>491</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5036</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>5381</v>
+        <v>4360</v>
       </c>
       <c r="D2" t="n">
-        <v>15916</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5477</v>
+        <v>495</v>
       </c>
       <c r="C3" t="n">
-        <v>11152</v>
+        <v>6129</v>
       </c>
       <c r="D3" t="n">
-        <v>12085</v>
+        <v>9991</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2784</v>
+        <v>723</v>
       </c>
       <c r="C4" t="n">
-        <v>11506</v>
+        <v>7638</v>
       </c>
       <c r="D4" t="n">
-        <v>6186</v>
+        <v>8492</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1638</v>
+        <v>718</v>
       </c>
       <c r="C5" t="n">
-        <v>7259</v>
+        <v>9482</v>
       </c>
       <c r="D5" t="n">
-        <v>2256</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>4076</v>
+        <v>8111</v>
       </c>
       <c r="D6" t="n">
-        <v>804</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>2622</v>
+        <v>4031</v>
       </c>
       <c r="D7" t="n">
-        <v>495</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1417</v>
+        <v>1249</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>415</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4799</v>
+        <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>9111</v>
+        <v>8661</v>
       </c>
       <c r="D2" t="n">
-        <v>13216</v>
+        <v>10768</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4451</v>
+        <v>340</v>
       </c>
       <c r="C3" t="n">
-        <v>7612</v>
+        <v>4792</v>
       </c>
       <c r="D3" t="n">
-        <v>11793</v>
+        <v>9180</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3360</v>
+        <v>554</v>
       </c>
       <c r="C4" t="n">
-        <v>11100</v>
+        <v>6798</v>
       </c>
       <c r="D4" t="n">
-        <v>6960</v>
+        <v>8464</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1876</v>
+        <v>666</v>
       </c>
       <c r="C5" t="n">
-        <v>9024</v>
+        <v>8488</v>
       </c>
       <c r="D5" t="n">
-        <v>2791</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1151</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>5452</v>
+        <v>8603</v>
       </c>
       <c r="D6" t="n">
-        <v>1002</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>3219</v>
+        <v>5708</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1902</v>
+        <v>2296</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>857</v>
+        <v>704</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2930</v>
+        <v>128</v>
       </c>
       <c r="C2" t="n">
-        <v>4420</v>
+        <v>4781</v>
       </c>
       <c r="D2" t="n">
-        <v>9211</v>
+        <v>7839</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4373</v>
+        <v>474</v>
       </c>
       <c r="C3" t="n">
-        <v>7884</v>
+        <v>6150</v>
       </c>
       <c r="D3" t="n">
-        <v>11676</v>
+        <v>10075</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3699</v>
+        <v>891</v>
       </c>
       <c r="C4" t="n">
-        <v>10863</v>
+        <v>9568</v>
       </c>
       <c r="D4" t="n">
-        <v>7553</v>
+        <v>8749</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1968</v>
+        <v>468</v>
       </c>
       <c r="C5" t="n">
-        <v>10961</v>
+        <v>12280</v>
       </c>
       <c r="D5" t="n">
-        <v>2944</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>6247</v>
+        <v>7448</v>
       </c>
       <c r="D6" t="n">
-        <v>994</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>3405</v>
+        <v>2250</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1380</v>
+        <v>689</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3312</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>4096</v>
+        <v>2538</v>
       </c>
       <c r="D2" t="n">
-        <v>11745</v>
+        <v>5495</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3224</v>
+        <v>284</v>
       </c>
       <c r="C3" t="n">
-        <v>5708</v>
+        <v>4883</v>
       </c>
       <c r="D3" t="n">
-        <v>10594</v>
+        <v>9063</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3495</v>
+        <v>598</v>
       </c>
       <c r="C4" t="n">
-        <v>9292</v>
+        <v>7413</v>
       </c>
       <c r="D4" t="n">
-        <v>7956</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2344</v>
+        <v>444</v>
       </c>
       <c r="C5" t="n">
-        <v>10795</v>
+        <v>9794</v>
       </c>
       <c r="D5" t="n">
-        <v>3518</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1190</v>
+        <v>166</v>
       </c>
       <c r="C6" t="n">
-        <v>8153</v>
+        <v>7747</v>
       </c>
       <c r="D6" t="n">
-        <v>1252</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
-        <v>4556</v>
+        <v>3064</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>2101</v>
+        <v>795</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>119</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2300</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>3510</v>
+        <v>10098</v>
       </c>
       <c r="D2" t="n">
-        <v>9058</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2852</v>
+        <v>169</v>
       </c>
       <c r="C3" t="n">
-        <v>4664</v>
+        <v>3246</v>
       </c>
       <c r="D3" t="n">
-        <v>10163</v>
+        <v>7882</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3121</v>
+        <v>399</v>
       </c>
       <c r="C4" t="n">
-        <v>7990</v>
+        <v>5922</v>
       </c>
       <c r="D4" t="n">
-        <v>8119</v>
+        <v>8218</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2552</v>
+        <v>465</v>
       </c>
       <c r="C5" t="n">
-        <v>10376</v>
+        <v>8378</v>
       </c>
       <c r="D5" t="n">
-        <v>3947</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1368</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>9261</v>
+        <v>8743</v>
       </c>
       <c r="D6" t="n">
-        <v>1435</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>5677</v>
+        <v>5265</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>2667</v>
+        <v>1825</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>712</v>
+        <v>487</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3984</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>8314</v>
+        <v>12080</v>
       </c>
       <c r="D2" t="n">
-        <v>9314</v>
+        <v>19887</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2247</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>3776</v>
+        <v>5597</v>
       </c>
       <c r="D3" t="n">
-        <v>9405</v>
+        <v>7408</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2660</v>
+        <v>264</v>
       </c>
       <c r="C4" t="n">
-        <v>6482</v>
+        <v>4514</v>
       </c>
       <c r="D4" t="n">
-        <v>8146</v>
+        <v>7913</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2498</v>
+        <v>402</v>
       </c>
       <c r="C5" t="n">
-        <v>9243</v>
+        <v>6991</v>
       </c>
       <c r="D5" t="n">
-        <v>4309</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1619</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>9593</v>
+        <v>8492</v>
       </c>
       <c r="D6" t="n">
-        <v>1730</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>6939</v>
+        <v>6796</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>924</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>3695</v>
+        <v>3273</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1312</v>
+        <v>1024</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6602</v>
+        <v>2199</v>
       </c>
       <c r="C2" t="n">
-        <v>14212</v>
+        <v>11635</v>
       </c>
       <c r="D2" t="n">
-        <v>5423</v>
+        <v>12710</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2912</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
-        <v>4922</v>
+        <v>17313</v>
       </c>
       <c r="D2" t="n">
-        <v>6929</v>
+        <v>17265</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3107</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>5126</v>
+        <v>7304</v>
       </c>
       <c r="D3" t="n">
-        <v>10175</v>
+        <v>8431</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3644</v>
+        <v>176</v>
       </c>
       <c r="C4" t="n">
-        <v>9556</v>
+        <v>4887</v>
       </c>
       <c r="D4" t="n">
-        <v>8228</v>
+        <v>7523</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>326</v>
       </c>
       <c r="C5" t="n">
-        <v>13570</v>
+        <v>5755</v>
       </c>
       <c r="D5" t="n">
-        <v>3967</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>495</v>
+        <v>320</v>
       </c>
       <c r="C6" t="n">
-        <v>8398</v>
+        <v>7812</v>
       </c>
       <c r="D6" t="n">
-        <v>1459</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>3621</v>
+        <v>7391</v>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1285</v>
+        <v>4618</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>1829</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>551</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8305</v>
+        <v>3367</v>
       </c>
       <c r="C2" t="n">
-        <v>6992</v>
+        <v>7825</v>
       </c>
       <c r="D2" t="n">
-        <v>8223</v>
+        <v>25674</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2804</v>
+        <v>730</v>
       </c>
       <c r="C3" t="n">
-        <v>7162</v>
+        <v>4594</v>
       </c>
       <c r="D3" t="n">
-        <v>1550</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6019</v>
+        <v>1826</v>
       </c>
       <c r="C2" t="n">
-        <v>4955</v>
+        <v>3987</v>
       </c>
       <c r="D2" t="n">
-        <v>13481</v>
+        <v>22256</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4559</v>
+        <v>1740</v>
       </c>
       <c r="C3" t="n">
-        <v>6093</v>
+        <v>5612</v>
       </c>
       <c r="D3" t="n">
-        <v>2556</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1252</v>
+        <v>365</v>
       </c>
       <c r="C4" t="n">
-        <v>4240</v>
+        <v>2914</v>
       </c>
       <c r="D4" t="n">
-        <v>1493</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7333</v>
+        <v>1106</v>
       </c>
       <c r="C2" t="n">
-        <v>6672</v>
+        <v>8998</v>
       </c>
       <c r="D2" t="n">
-        <v>15069</v>
+        <v>21352</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4340</v>
+        <v>1471</v>
       </c>
       <c r="C3" t="n">
-        <v>4755</v>
+        <v>4024</v>
       </c>
       <c r="D3" t="n">
-        <v>4119</v>
+        <v>8498</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2468</v>
+        <v>926</v>
       </c>
       <c r="C4" t="n">
-        <v>5142</v>
+        <v>4459</v>
       </c>
       <c r="D4" t="n">
-        <v>1651</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>563</v>
+        <v>203</v>
       </c>
       <c r="C5" t="n">
-        <v>2416</v>
+        <v>1762</v>
       </c>
       <c r="D5" t="n">
-        <v>1203</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6706</v>
+        <v>1297</v>
       </c>
       <c r="C2" t="n">
         <v>11039</v>
       </c>
       <c r="D2" t="n">
-        <v>17517</v>
+        <v>20589</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4695</v>
+        <v>1081</v>
       </c>
       <c r="C3" t="n">
-        <v>4989</v>
+        <v>5830</v>
       </c>
       <c r="D3" t="n">
-        <v>5493</v>
+        <v>9942</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2857</v>
+        <v>1024</v>
       </c>
       <c r="C4" t="n">
-        <v>4781</v>
+        <v>4119</v>
       </c>
       <c r="D4" t="n">
-        <v>2050</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>479</v>
       </c>
       <c r="C5" t="n">
-        <v>3778</v>
+        <v>3201</v>
       </c>
       <c r="D5" t="n">
-        <v>1232</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>303</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>1355</v>
+        <v>1048</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6650</v>
+        <v>2012</v>
       </c>
       <c r="C2" t="n">
-        <v>10860</v>
+        <v>16763</v>
       </c>
       <c r="D2" t="n">
-        <v>16542</v>
+        <v>24796</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4107</v>
+        <v>975</v>
       </c>
       <c r="C3" t="n">
-        <v>6574</v>
+        <v>7408</v>
       </c>
       <c r="D3" t="n">
-        <v>6523</v>
+        <v>10860</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2310</v>
+        <v>912</v>
       </c>
       <c r="C4" t="n">
-        <v>4003</v>
+        <v>4953</v>
       </c>
       <c r="D4" t="n">
-        <v>2281</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1057</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>3097</v>
+        <v>3579</v>
       </c>
       <c r="D5" t="n">
-        <v>1072</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>362</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>1719</v>
+        <v>2131</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>528</v>
+        <v>670</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5753</v>
+        <v>1695</v>
       </c>
       <c r="C2" t="n">
-        <v>12032</v>
+        <v>13276</v>
       </c>
       <c r="D2" t="n">
-        <v>14228</v>
+        <v>19251</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4445</v>
+        <v>1173</v>
       </c>
       <c r="C3" t="n">
-        <v>7808</v>
+        <v>10521</v>
       </c>
       <c r="D3" t="n">
-        <v>7726</v>
+        <v>12119</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2803</v>
+        <v>816</v>
       </c>
       <c r="C4" t="n">
-        <v>5474</v>
+        <v>6027</v>
       </c>
       <c r="D4" t="n">
-        <v>3044</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>3563</v>
+        <v>4177</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>655</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>2478</v>
+        <v>2790</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>1193</v>
+        <v>1336</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4804</v>
+        <v>1545</v>
       </c>
       <c r="C2" t="n">
-        <v>10930</v>
+        <v>8284</v>
       </c>
       <c r="D2" t="n">
-        <v>20988</v>
+        <v>15171</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4178</v>
+        <v>1504</v>
       </c>
       <c r="C3" t="n">
-        <v>8731</v>
+        <v>14461</v>
       </c>
       <c r="D3" t="n">
-        <v>8210</v>
+        <v>13410</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3083</v>
+        <v>623</v>
       </c>
       <c r="C4" t="n">
-        <v>6659</v>
+        <v>7770</v>
       </c>
       <c r="D4" t="n">
-        <v>3850</v>
+        <v>5158</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1875</v>
+        <v>364</v>
       </c>
       <c r="C5" t="n">
-        <v>4516</v>
+        <v>2734</v>
       </c>
       <c r="D5" t="n">
-        <v>1565</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>955</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>2988</v>
+        <v>1309</v>
       </c>
       <c r="D6" t="n">
-        <v>869</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>1859</v>
+        <v>457</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>789</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
